--- a/data/trans_dic/IP31KM09_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM09_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,13; 95,3</t>
+          <t>67,91; 95,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,37; 95,85</t>
+          <t>87,16; 95,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,42; 94,29</t>
+          <t>80,38; 94,33</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,45; 97,78</t>
+          <t>91,87; 97,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,13; 96,76</t>
+          <t>94,18; 98,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,26; 96,98</t>
+          <t>93,41; 97,17</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,68; 95,4</t>
+          <t>89,16; 96,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,42; 96,72</t>
+          <t>85,24; 93,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,09; 95,17</t>
+          <t>88,54; 94,23</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,85; 94,66</t>
+          <t>87,35; 94,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,43; 94,98</t>
+          <t>87,55; 94,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,55; 93,97</t>
+          <t>88,66; 94,05</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,03; 94,62</t>
+          <t>88,43; 94,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,42; 94,63</t>
+          <t>90,78; 94,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,92; 94,01</t>
+          <t>90,52; 94,02</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>172</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>104630</t>
+          <t>108357</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>119550</t>
+          <t>109284</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224180</t>
+          <t>217641</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98406; 108886</t>
+          <t>83465; 117948</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86703; 131141</t>
+          <t>103371; 112972</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>189366; 236736</t>
+          <t>194117; 227794</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>256</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>179112</t>
+          <t>219773</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>234919</t>
+          <t>174206</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414030</t>
+          <t>393978</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>173923; 181977</t>
+          <t>212441; 224712</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>225572; 239507</t>
+          <t>170091; 177148</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>404416; 420520</t>
+          <t>384711; 400176</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>201</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>172997</t>
+          <t>156218</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>172360</t>
+          <t>139336</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>345358</t>
+          <t>295554</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>165061; 179599</t>
+          <t>148476; 160736</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>163727; 177084</t>
+          <t>132158; 145012</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>334550; 353398</t>
+          <t>284699; 302998</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>215</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>150638</t>
+          <t>152510</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>162480</t>
+          <t>150321</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313118</t>
+          <t>302831</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>142883; 155741</t>
+          <t>145143; 157774</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>155024; 168400</t>
+          <t>143557; 155182</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>302705; 321209</t>
+          <t>292715; 310489</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>844</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>607377</t>
+          <t>636857</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>689310</t>
+          <t>573148</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1296687</t>
+          <t>1210004</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>594531; 618007</t>
+          <t>607353; 650829</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>643635; 704732</t>
+          <t>561227; 582761</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1256992; 1314187</t>
+          <t>1181271; 1226927</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM09_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM09_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que desayunan cereales o derivados (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>88,17%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>92,15%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>67,91; 95,97</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>87,16; 95,26</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>80,38; 94,33</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>95,04%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>95,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>91,87; 97,18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>94,18; 98,09</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>93,41; 97,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>89,87%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>91,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>89,16; 96,53</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>85,24; 93,53</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>88,54; 94,23</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>91,78%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>91,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>87,35; 94,95</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>87,55; 94,64</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>88,66; 94,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>88,43; 94,76</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>90,78; 94,27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>90,52; 94,02</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8816948947208234</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9214679944962427</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9012274581186303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>108357</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>109284</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>217641</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.6791477486072723</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.8716041763226029</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8038167337201366</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>83465; 117948</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>103371; 112972</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>194117; 227794</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9597396503015768</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.95256572467074</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9432705410870692</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9504057563858355</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.96463547810998</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9566456237613261</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>219773</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>174206</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>393978</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.9187016015614043</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9418496991187606</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9341439571992247</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>212441; 224712</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>170091; 177148</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>384711; 400176</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9717656854520795</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9809262475147558</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9716947934317979</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9381205507957232</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8987225424084426</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9191250419845483</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>156218</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>139336</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>295554</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.8916282594104648</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.8524261242456808</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8853673924373825</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>148476; 160736</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>132158; 145012</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>284699; 302998</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.965256804270319</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9353330118613763</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9422746328761556</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9178216235999767</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9167091062431637</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9172690480648716</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>152510</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>150321</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>302831</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8734855969951578</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8754615332831898</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.886628561053793</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>145143; 157774</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>143557; 155182</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>292715; 310489</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9495031379367893</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9463519760715868</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9404648009160962</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>844</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.9272492928201883</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9271116768121139</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9271841026066828</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>636857</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>573148</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1210004</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8842917752124185</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.9078286603310789</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.9051669748772317</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>607353; 650829</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>561227; 582761</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1181271; 1226927</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9475922409419725</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9426622292671428</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9401513816581489</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que desayunan cereales o derivados (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>153</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>172</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>108357</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>109284</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>217641</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>83465</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>103371</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>194117</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>117948</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>112972</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>227794</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>308</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>256</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>219773</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>174206</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>393978</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>212441</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>170091</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>384711</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>224712</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>177148</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>400176</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>206</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>201</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>156218</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>139336</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>295554</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>148476</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>132158</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>284699</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>160736</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>145012</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>302998</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>212</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>152510</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>150321</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>302831</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>145143</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>143557</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>292715</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>157774</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>155182</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>310489</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>879</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>844</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>636857</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>573148</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1210004</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>607353</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>561227</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1181271</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>650829</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>582761</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1226927</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>